--- a/data/nzd0552/nzd0552.xlsx
+++ b/data/nzd0552/nzd0552.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G444"/>
+  <dimension ref="A1:G445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12404,6 +12404,33 @@
         <v>374.55</v>
       </c>
       <c r="G444" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>335.67</v>
+      </c>
+      <c r="C445" t="n">
+        <v>330.76</v>
+      </c>
+      <c r="D445" t="n">
+        <v>340.08</v>
+      </c>
+      <c r="E445" t="n">
+        <v>342.87</v>
+      </c>
+      <c r="F445" t="n">
+        <v>373.27</v>
+      </c>
+      <c r="G445" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12420,7 +12447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B518"/>
+  <dimension ref="A1:B519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17603,6 +17630,16 @@
       </c>
       <c r="B518" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>-0.91</v>
       </c>
     </row>
   </sheetData>
@@ -17771,28 +17808,28 @@
         <v>0.0333</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.467929053286556</v>
+        <v>-1.459484539736436</v>
       </c>
       <c r="J2" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K2" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1773127557745577</v>
+        <v>0.1761301192784234</v>
       </c>
       <c r="M2" t="n">
-        <v>18.13669975156834</v>
+        <v>18.13522894270211</v>
       </c>
       <c r="N2" t="n">
-        <v>580.6690609205616</v>
+        <v>580.2108999793064</v>
       </c>
       <c r="O2" t="n">
-        <v>24.09707577530024</v>
+        <v>24.08756733211775</v>
       </c>
       <c r="P2" t="n">
-        <v>354.9204316984221</v>
+        <v>354.8360223346774</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17849,28 +17886,28 @@
         <v>0.0312</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.476306772102417</v>
+        <v>-1.468227997353975</v>
       </c>
       <c r="J3" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K3" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2745372519798479</v>
+        <v>0.2728644942666859</v>
       </c>
       <c r="M3" t="n">
-        <v>13.26430242653587</v>
+        <v>13.26631270032793</v>
       </c>
       <c r="N3" t="n">
-        <v>333.6705864788249</v>
+        <v>333.6884106068321</v>
       </c>
       <c r="O3" t="n">
-        <v>18.26665230628822</v>
+        <v>18.26714018687195</v>
       </c>
       <c r="P3" t="n">
-        <v>351.1775042965509</v>
+        <v>351.0964623137706</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17927,28 +17964,28 @@
         <v>0.0354</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.403443989345355</v>
+        <v>-1.391957454895123</v>
       </c>
       <c r="J4" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K4" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2280445704200825</v>
+        <v>0.2253087997032237</v>
       </c>
       <c r="M4" t="n">
-        <v>14.64053954042068</v>
+        <v>14.63717382396462</v>
       </c>
       <c r="N4" t="n">
-        <v>386.2900535974324</v>
+        <v>386.9797045094571</v>
       </c>
       <c r="O4" t="n">
-        <v>19.65426298789737</v>
+        <v>19.67179972726078</v>
       </c>
       <c r="P4" t="n">
-        <v>350.7546610743511</v>
+        <v>350.6394342539348</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18005,28 +18042,28 @@
         <v>0.0309</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.332833001148477</v>
+        <v>-1.31772835568706</v>
       </c>
       <c r="J5" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K5" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1307020613513507</v>
+        <v>0.1282380938166773</v>
       </c>
       <c r="M5" t="n">
-        <v>18.91064910254539</v>
+        <v>18.91441482460376</v>
       </c>
       <c r="N5" t="n">
-        <v>683.0568076311431</v>
+        <v>684.2112265365205</v>
       </c>
       <c r="O5" t="n">
-        <v>26.13535550994367</v>
+        <v>26.15743157377116</v>
       </c>
       <c r="P5" t="n">
-        <v>343.3806708381547</v>
+        <v>343.2290142522671</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18083,28 +18120,28 @@
         <v>0.0385</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.137162575899364</v>
+        <v>-0.1346025212980922</v>
       </c>
       <c r="J6" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K6" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008080702391566774</v>
+        <v>0.007817664935720559</v>
       </c>
       <c r="M6" t="n">
-        <v>8.752946669522773</v>
+        <v>8.744443247290405</v>
       </c>
       <c r="N6" t="n">
-        <v>132.330161456238</v>
+        <v>132.1073729138749</v>
       </c>
       <c r="O6" t="n">
-        <v>11.50348475272767</v>
+        <v>11.49379714950089</v>
       </c>
       <c r="P6" t="n">
-        <v>371.0508673657592</v>
+        <v>371.025004775187</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18142,7 +18179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G444"/>
+  <dimension ref="A1:G445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34533,6 +34570,43 @@
         </is>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>-46.60353789306349,169.4206354523128</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>-46.60355398154701,169.41973714957425</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>-46.60369773005098,169.41885118518007</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>-46.603782896596236,169.41795955807865</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>-46.60411575776461,169.41709186270322</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0552/nzd0552.xlsx
+++ b/data/nzd0552/nzd0552.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G445"/>
+  <dimension ref="A1:G446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12431,6 +12431,33 @@
         <v>373.27</v>
       </c>
       <c r="G445" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:14:53+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>335.4</v>
+      </c>
+      <c r="C446" t="n">
+        <v>330.81</v>
+      </c>
+      <c r="D446" t="n">
+        <v>338.84</v>
+      </c>
+      <c r="E446" t="n">
+        <v>341.29</v>
+      </c>
+      <c r="F446" t="n">
+        <v>369.12</v>
+      </c>
+      <c r="G446" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12447,7 +12474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B519"/>
+  <dimension ref="A1:B520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17640,6 +17667,16 @@
       </c>
       <c r="B519" t="n">
         <v>-0.91</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -17808,28 +17845,28 @@
         <v>0.0333</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.459484539736436</v>
+        <v>-1.451156072414496</v>
       </c>
       <c r="J2" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K2" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1761301192784234</v>
+        <v>0.1749778215758807</v>
       </c>
       <c r="M2" t="n">
-        <v>18.13522894270211</v>
+        <v>18.1333086772931</v>
       </c>
       <c r="N2" t="n">
-        <v>580.2108999793064</v>
+        <v>579.7305898066277</v>
       </c>
       <c r="O2" t="n">
-        <v>24.08756733211775</v>
+        <v>24.07759518321188</v>
       </c>
       <c r="P2" t="n">
-        <v>354.8360223346774</v>
+        <v>354.7524369063885</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17886,28 +17923,28 @@
         <v>0.0312</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.468227997353975</v>
+        <v>-1.460120708347241</v>
       </c>
       <c r="J3" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K3" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2728644942666859</v>
+        <v>0.2711828729980661</v>
       </c>
       <c r="M3" t="n">
-        <v>13.26631270032793</v>
+        <v>13.26813974186639</v>
       </c>
       <c r="N3" t="n">
-        <v>333.6884106068321</v>
+        <v>333.7105998968049</v>
       </c>
       <c r="O3" t="n">
-        <v>18.26714018687195</v>
+        <v>18.26774753210709</v>
       </c>
       <c r="P3" t="n">
-        <v>351.0964623137706</v>
+        <v>351.0148054986818</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17964,28 +18001,28 @@
         <v>0.0354</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.391957454895123</v>
+        <v>-1.381033763084427</v>
       </c>
       <c r="J4" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K4" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2253087997032237</v>
+        <v>0.2227895484676077</v>
       </c>
       <c r="M4" t="n">
-        <v>14.63717382396462</v>
+        <v>14.63200601166583</v>
       </c>
       <c r="N4" t="n">
-        <v>386.9797045094571</v>
+        <v>387.515055078648</v>
       </c>
       <c r="O4" t="n">
-        <v>19.67179972726078</v>
+        <v>19.68540208069543</v>
       </c>
       <c r="P4" t="n">
-        <v>350.6394342539348</v>
+        <v>350.5294105602523</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18042,28 +18079,28 @@
         <v>0.0309</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.31772835568706</v>
+        <v>-1.303358773814635</v>
       </c>
       <c r="J5" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K5" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1282380938166773</v>
+        <v>0.125955739556867</v>
       </c>
       <c r="M5" t="n">
-        <v>18.91441482460376</v>
+        <v>18.9154415910565</v>
       </c>
       <c r="N5" t="n">
-        <v>684.2112265365205</v>
+        <v>685.1014494840618</v>
       </c>
       <c r="O5" t="n">
-        <v>26.15743157377116</v>
+        <v>26.17444267762089</v>
       </c>
       <c r="P5" t="n">
-        <v>343.2290142522671</v>
+        <v>343.0841569027907</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18120,28 +18157,28 @@
         <v>0.0385</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1346025212980922</v>
+        <v>-0.133876202302695</v>
       </c>
       <c r="J6" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K6" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007817664935720559</v>
+        <v>0.00777177379677596</v>
       </c>
       <c r="M6" t="n">
-        <v>8.744443247290405</v>
+        <v>8.727876143774902</v>
       </c>
       <c r="N6" t="n">
-        <v>132.1073729138749</v>
+        <v>131.8153059498455</v>
       </c>
       <c r="O6" t="n">
-        <v>11.49379714950089</v>
+        <v>11.48108470266836</v>
       </c>
       <c r="P6" t="n">
-        <v>371.025004775187</v>
+        <v>371.0176379712815</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18179,7 +18216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G445"/>
+  <dimension ref="A1:G446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34607,6 +34644,43 @@
         </is>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:14:53+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>-46.60353547084135,169.4206352181692</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>-46.60355443010669,169.4197371929291</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>-46.60368660577037,169.41885011010422</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-46.60376872210896,169.41795818838324</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>-46.60407852730681,169.4170882654822</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0552/nzd0552.xlsx
+++ b/data/nzd0552/nzd0552.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G446"/>
+  <dimension ref="A1:G447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12460,6 +12460,33 @@
       <c r="G446" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:55+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>336.62</v>
+      </c>
+      <c r="C447" t="n">
+        <v>329.83</v>
+      </c>
+      <c r="D447" t="n">
+        <v>339.6</v>
+      </c>
+      <c r="E447" t="n">
+        <v>341.09</v>
+      </c>
+      <c r="F447" t="n">
+        <v>364.51</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B520"/>
+  <dimension ref="A1:B521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17677,6 +17704,16 @@
       </c>
       <c r="B520" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>-0.95</v>
       </c>
     </row>
   </sheetData>
@@ -17845,28 +17882,28 @@
         <v>0.0333</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.451156072414496</v>
+        <v>-1.442204840629228</v>
       </c>
       <c r="J2" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K2" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1749778215758807</v>
+        <v>0.1736822112787842</v>
       </c>
       <c r="M2" t="n">
-        <v>18.1333086772931</v>
+        <v>18.13449353829781</v>
       </c>
       <c r="N2" t="n">
-        <v>579.7305898066277</v>
+        <v>579.3679823143157</v>
       </c>
       <c r="O2" t="n">
-        <v>24.07759518321188</v>
+        <v>24.0700640280477</v>
       </c>
       <c r="P2" t="n">
-        <v>354.7524369063885</v>
+        <v>354.6619781944452</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17923,28 +17960,28 @@
         <v>0.0312</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.460120708347241</v>
+        <v>-1.452351826649531</v>
       </c>
       <c r="J3" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K3" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2711828729980661</v>
+        <v>0.2696484138118238</v>
       </c>
       <c r="M3" t="n">
-        <v>13.26813974186639</v>
+        <v>13.2683433831808</v>
       </c>
       <c r="N3" t="n">
-        <v>333.7105998968049</v>
+        <v>333.6603214503888</v>
       </c>
       <c r="O3" t="n">
-        <v>18.26774753210709</v>
+        <v>18.26637132685057</v>
       </c>
       <c r="P3" t="n">
-        <v>351.0148054986818</v>
+        <v>350.936013542559</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18001,28 +18038,28 @@
         <v>0.0354</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.381033763084427</v>
+        <v>-1.369691615777011</v>
       </c>
       <c r="J4" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K4" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2227895484676077</v>
+        <v>0.2201412116463025</v>
       </c>
       <c r="M4" t="n">
-        <v>14.63200601166583</v>
+        <v>14.62728838428536</v>
       </c>
       <c r="N4" t="n">
-        <v>387.515055078648</v>
+        <v>388.1387467799206</v>
       </c>
       <c r="O4" t="n">
-        <v>19.68540208069543</v>
+        <v>19.70123718906812</v>
       </c>
       <c r="P4" t="n">
-        <v>350.5294105602523</v>
+        <v>350.4143785636591</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18079,28 +18116,28 @@
         <v>0.0309</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.303358773814635</v>
+        <v>-1.289003700794739</v>
       </c>
       <c r="J5" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K5" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.125955739556867</v>
+        <v>0.1237008005715656</v>
       </c>
       <c r="M5" t="n">
-        <v>18.9154415910565</v>
+        <v>18.91562566238954</v>
       </c>
       <c r="N5" t="n">
-        <v>685.1014494840618</v>
+        <v>685.9521710292482</v>
       </c>
       <c r="O5" t="n">
-        <v>26.17444267762089</v>
+        <v>26.1906886322076</v>
       </c>
       <c r="P5" t="n">
-        <v>343.0841569027907</v>
+        <v>342.9384442632075</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18157,28 +18194,28 @@
         <v>0.0385</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.133876202302695</v>
+        <v>-0.1351748185617948</v>
       </c>
       <c r="J6" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K6" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00777177379677596</v>
+        <v>0.007960487261534199</v>
       </c>
       <c r="M6" t="n">
-        <v>8.727876143774902</v>
+        <v>8.715796391292931</v>
       </c>
       <c r="N6" t="n">
-        <v>131.8153059498455</v>
+        <v>131.5377725822312</v>
       </c>
       <c r="O6" t="n">
-        <v>11.48108470266836</v>
+        <v>11.46899178577747</v>
       </c>
       <c r="P6" t="n">
-        <v>371.0176379712815</v>
+        <v>371.0308996728228</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18216,7 +18253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G446"/>
+  <dimension ref="A1:G447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34681,6 +34718,43 @@
         </is>
       </c>
     </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:55+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>-46.60354641569699,169.42063627615164</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>-46.603545638336904,169.4197363431748</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>-46.60369342387784,169.41885076902165</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-46.60376692787008,169.41795801500413</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>-46.60403717009928,169.41708426953707</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0552/nzd0552.xlsx
+++ b/data/nzd0552/nzd0552.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G447"/>
+  <dimension ref="A1:G449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12485,6 +12485,60 @@
         <v>364.51</v>
       </c>
       <c r="G447" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>333.52</v>
+      </c>
+      <c r="C448" t="n">
+        <v>329.71</v>
+      </c>
+      <c r="D448" t="n">
+        <v>340.12</v>
+      </c>
+      <c r="E448" t="n">
+        <v>348.57</v>
+      </c>
+      <c r="F448" t="n">
+        <v>354.03</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>333.52</v>
+      </c>
+      <c r="C449" t="n">
+        <v>329.71</v>
+      </c>
+      <c r="D449" t="n">
+        <v>340.12</v>
+      </c>
+      <c r="E449" t="n">
+        <v>350.41</v>
+      </c>
+      <c r="F449" t="n">
+        <v>354.93</v>
+      </c>
+      <c r="G449" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12501,7 +12555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B521"/>
+  <dimension ref="A1:B523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17714,6 +17768,26 @@
       </c>
       <c r="B521" t="n">
         <v>-0.95</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -17882,28 +17956,28 @@
         <v>0.0333</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.442204840629228</v>
+        <v>-1.427126251120542</v>
       </c>
       <c r="J2" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K2" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1736822112787842</v>
+        <v>0.1717768653188849</v>
       </c>
       <c r="M2" t="n">
-        <v>18.13449353829781</v>
+        <v>18.12335885698584</v>
       </c>
       <c r="N2" t="n">
-        <v>579.3679823143157</v>
+        <v>578.1141372390199</v>
       </c>
       <c r="O2" t="n">
-        <v>24.0700640280477</v>
+        <v>24.04400418480707</v>
       </c>
       <c r="P2" t="n">
-        <v>354.6619781944452</v>
+        <v>354.5090154820115</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17960,28 +18034,28 @@
         <v>0.0312</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.452351826649531</v>
+        <v>-1.437032098397534</v>
       </c>
       <c r="J3" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K3" t="n">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2696484138118238</v>
+        <v>0.2666434904860208</v>
       </c>
       <c r="M3" t="n">
-        <v>13.2683433831808</v>
+        <v>13.26868847390272</v>
       </c>
       <c r="N3" t="n">
-        <v>333.6603214503888</v>
+        <v>333.5304892665246</v>
       </c>
       <c r="O3" t="n">
-        <v>18.26637132685057</v>
+        <v>18.26281712295572</v>
       </c>
       <c r="P3" t="n">
-        <v>350.936013542559</v>
+        <v>350.7800460594572</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18038,28 +18112,28 @@
         <v>0.0354</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.369691615777011</v>
+        <v>-1.346776271712842</v>
       </c>
       <c r="J4" t="n">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K4" t="n">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2201412116463025</v>
+        <v>0.2147586607204421</v>
       </c>
       <c r="M4" t="n">
-        <v>14.62728838428536</v>
+        <v>14.61777512625216</v>
       </c>
       <c r="N4" t="n">
-        <v>388.1387467799206</v>
+        <v>389.4590657250592</v>
       </c>
       <c r="O4" t="n">
-        <v>19.70123718906812</v>
+        <v>19.73471726995498</v>
       </c>
       <c r="P4" t="n">
-        <v>350.4143785636591</v>
+        <v>350.1810815735293</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18116,28 +18190,28 @@
         <v>0.0309</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.289003700794739</v>
+        <v>-1.25327553523256</v>
       </c>
       <c r="J5" t="n">
+        <v>448</v>
+      </c>
+      <c r="K5" t="n">
         <v>446</v>
       </c>
-      <c r="K5" t="n">
-        <v>444</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1237008005715656</v>
+        <v>0.1176505987512124</v>
       </c>
       <c r="M5" t="n">
-        <v>18.91562566238954</v>
+        <v>18.93825561415153</v>
       </c>
       <c r="N5" t="n">
-        <v>685.9521710292482</v>
+        <v>690.3095243055777</v>
       </c>
       <c r="O5" t="n">
-        <v>26.1906886322076</v>
+        <v>26.27374210700824</v>
       </c>
       <c r="P5" t="n">
-        <v>342.9384442632075</v>
+        <v>342.5743913626989</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18194,28 +18268,28 @@
         <v>0.0385</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1351748185617948</v>
+        <v>-0.1465197626790909</v>
       </c>
       <c r="J6" t="n">
+        <v>448</v>
+      </c>
+      <c r="K6" t="n">
         <v>446</v>
       </c>
-      <c r="K6" t="n">
-        <v>444</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.007960487261534199</v>
+        <v>0.009380675076295142</v>
       </c>
       <c r="M6" t="n">
-        <v>8.715796391292931</v>
+        <v>8.742768266970407</v>
       </c>
       <c r="N6" t="n">
-        <v>131.5377725822312</v>
+        <v>131.6888547638699</v>
       </c>
       <c r="O6" t="n">
-        <v>11.46899178577747</v>
+        <v>11.47557644582048</v>
       </c>
       <c r="P6" t="n">
-        <v>371.0308996728228</v>
+        <v>371.147190119395</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18253,7 +18327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G447"/>
+  <dimension ref="A1:G449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34755,6 +34829,80 @@
         </is>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>-46.60351860499821,169.42063358783616</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>-46.60354456179367,169.41973623912327</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>-46.603698088898746,169.41885121985996</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-46.60383403240455,169.41796449938892</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>-46.60394315197812,169.41707518549543</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:21+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>-46.60351860499821,169.42063358783616</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>-46.60354456179367,169.41973623912327</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>-46.603698088898746,169.41885121985996</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-46.60385053940225,169.41796609447994</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>-46.603951226053475,169.41707596561264</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0552/nzd0552.xlsx
+++ b/data/nzd0552/nzd0552.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G449"/>
+  <dimension ref="A1:G453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12524,13 +12524,13 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>333.52</v>
+        <v>338.18</v>
       </c>
       <c r="C449" t="n">
-        <v>329.71</v>
+        <v>334.65</v>
       </c>
       <c r="D449" t="n">
-        <v>340.12</v>
+        <v>343.5</v>
       </c>
       <c r="E449" t="n">
         <v>350.41</v>
@@ -12541,6 +12541,114 @@
       <c r="G449" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="C450" t="n">
+        <v>335.49</v>
+      </c>
+      <c r="D450" t="n">
+        <v>344.06</v>
+      </c>
+      <c r="E450" t="n">
+        <v>348.23</v>
+      </c>
+      <c r="F450" t="n">
+        <v>352.81</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>339.04</v>
+      </c>
+      <c r="C451" t="n">
+        <v>336.39</v>
+      </c>
+      <c r="D451" t="n">
+        <v>344.4</v>
+      </c>
+      <c r="E451" t="n">
+        <v>346.88</v>
+      </c>
+      <c r="F451" t="n">
+        <v>353.32</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>337.03</v>
+      </c>
+      <c r="C452" t="n">
+        <v>337.06</v>
+      </c>
+      <c r="D452" t="n">
+        <v>344.51</v>
+      </c>
+      <c r="E452" t="n">
+        <v>347.53</v>
+      </c>
+      <c r="F452" t="n">
+        <v>357.15</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>337.13</v>
+      </c>
+      <c r="C453" t="n">
+        <v>336.4</v>
+      </c>
+      <c r="D453" t="n">
+        <v>343.97</v>
+      </c>
+      <c r="E453" t="n">
+        <v>346.66</v>
+      </c>
+      <c r="F453" t="n">
+        <v>358.53</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B523"/>
+  <dimension ref="A1:B528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17788,6 +17896,56 @@
       </c>
       <c r="B523" t="n">
         <v>0.47</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>-0.72</v>
       </c>
     </row>
   </sheetData>
@@ -17956,28 +18114,28 @@
         <v>0.0333</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.427126251120542</v>
+        <v>-1.388801619777452</v>
       </c>
       <c r="J2" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K2" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1717768653188849</v>
+        <v>0.165847113086404</v>
       </c>
       <c r="M2" t="n">
-        <v>18.12335885698584</v>
+        <v>18.13982916025102</v>
       </c>
       <c r="N2" t="n">
-        <v>578.1141372390199</v>
+        <v>577.3417471376472</v>
       </c>
       <c r="O2" t="n">
-        <v>24.04400418480707</v>
+        <v>24.02793680567783</v>
       </c>
       <c r="P2" t="n">
-        <v>354.5090154820115</v>
+        <v>354.1188042149492</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18034,28 +18192,28 @@
         <v>0.0312</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.437032098397534</v>
+        <v>-1.393849196876642</v>
       </c>
       <c r="J3" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K3" t="n">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2666434904860208</v>
+        <v>0.2555336420558417</v>
       </c>
       <c r="M3" t="n">
-        <v>13.26868847390272</v>
+        <v>13.31874019148117</v>
       </c>
       <c r="N3" t="n">
-        <v>333.5304892665246</v>
+        <v>336.0037142753085</v>
       </c>
       <c r="O3" t="n">
-        <v>18.26281712295572</v>
+        <v>18.33040409470856</v>
       </c>
       <c r="P3" t="n">
-        <v>350.7800460594572</v>
+        <v>350.3387652256853</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18112,28 +18270,28 @@
         <v>0.0354</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.346776271712842</v>
+        <v>-1.293879384639617</v>
       </c>
       <c r="J4" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K4" t="n">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2147586607204421</v>
+        <v>0.2013183064494253</v>
       </c>
       <c r="M4" t="n">
-        <v>14.61777512625216</v>
+        <v>14.61527548059223</v>
       </c>
       <c r="N4" t="n">
-        <v>389.4590657250592</v>
+        <v>394.2698396396655</v>
       </c>
       <c r="O4" t="n">
-        <v>19.73471726995498</v>
+        <v>19.85622924020736</v>
       </c>
       <c r="P4" t="n">
-        <v>350.1810815735293</v>
+        <v>349.6405081429111</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18190,28 +18348,28 @@
         <v>0.0309</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.25327553523256</v>
+        <v>-1.187829836347038</v>
       </c>
       <c r="J5" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K5" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1176505987512124</v>
+        <v>0.1070953109369739</v>
       </c>
       <c r="M5" t="n">
-        <v>18.93825561415153</v>
+        <v>18.97274239078093</v>
       </c>
       <c r="N5" t="n">
-        <v>690.3095243055777</v>
+        <v>696.8807692184204</v>
       </c>
       <c r="O5" t="n">
-        <v>26.27374210700824</v>
+        <v>26.39849937436635</v>
       </c>
       <c r="P5" t="n">
-        <v>342.5743913626989</v>
+        <v>341.904977722722</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18268,28 +18426,28 @@
         <v>0.0385</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1465197626790909</v>
+        <v>-0.1667124794771275</v>
       </c>
       <c r="J6" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K6" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009380675076295142</v>
+        <v>0.01223512798053517</v>
       </c>
       <c r="M6" t="n">
-        <v>8.742768266970407</v>
+        <v>8.782897933627968</v>
       </c>
       <c r="N6" t="n">
-        <v>131.6888547638699</v>
+        <v>131.7671162201474</v>
       </c>
       <c r="O6" t="n">
-        <v>11.47557644582048</v>
+        <v>11.47898585329503</v>
       </c>
       <c r="P6" t="n">
-        <v>371.147190119395</v>
+        <v>371.3549294637586</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18327,7 +18485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G449"/>
+  <dimension ref="A1:G453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34874,17 +35032,17 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>-46.60351860499821,169.42063358783616</t>
+          <t>-46.60356041075826,169.42063762898206</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>-46.60354456179367,169.41973623912327</t>
+          <t>-46.603588879490275,169.41974052258038</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>-46.603698088898746,169.41885121985996</t>
+          <t>-46.60372841153452,169.41885415031027</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -34900,6 +35058,154 @@
       <c r="G449" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>-46.60355431034695,169.4206370392867</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>-46.60359641529292,169.419741250942</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>-46.60373343540316,169.41885463582886</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-46.60383098219845,169.4179642046439</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>-46.603932207120444,169.41707412800343</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>-46.60356812598434,169.4206383747734</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>-46.60360448936717,169.4197420313296</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>-46.60373648560911,169.41885493060806</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-46.60381887108599,169.41796303433307</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>-46.60393678242981,169.41707457006973</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>-46.60355009388616,169.42063663170316</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>-46.603610500066885,169.41974261228492</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>-46.60373747244044,169.4188550259778</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-46.60382470236236,169.41796359781603</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>-46.60397114210591,169.4170778899025</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>-46.603550991005484,169.42063671842308</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>-46.6036045790791,169.41974204000056</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-46.60373262799569,169.41885455779908</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-46.60381689742321,169.4179628436158</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>-46.60398352235471,169.41707908608313</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
